--- a/hanwha/downloads/해외자회사_공시실적.xlsx
+++ b/hanwha/downloads/해외자회사_공시실적.xlsx
@@ -841,7 +841,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="2:10" ht="32" customHeight="1">
+    <row r="4" spans="2:10" ht="32.25" customHeight="1">
       <c r="B4" s="3" t="s">
         <v>2</v>
       </c>
